--- a/excelCfg/item.xlsx
+++ b/excelCfg/item.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item" sheetId="1" r:id="R56dab8e5d5bf4a11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item" sheetId="1" r:id="Re9bbfbfa0fce46d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,15 +484,6 @@
     <x:t xml:space="preserve">I0XN</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">风火轮</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">哪吒核心专属</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">[专属] 基础生命 +450，移动速度 +65。冲锋火路唯一效果由 Lua 处理。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">I0XB</x:t>
   </x:si>
   <x:si>
@@ -548,12 +539,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">I0MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">哪吒碎片</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">[材料] 用于提交哪吒专属任务并兑换核心专属。</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">I0MB</x:t>
@@ -3278,17 +3263,17 @@
       <x:c r="B25" s="6" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="C25" s="6" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D25" s="6" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="E25" s="6" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F25" s="6" t="s">
-        <x:v>160</x:v>
+      <x:c r="C25" s="6" t="str">
+        <x:v>射日神弓</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>后羿核心专属</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str">
+        <x:v>射日神弓</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>[专属] 后羿持有时，金乌灼痕爆发伤害 +30%，范围 +90。</x:v>
       </x:c>
       <x:c r="G25" s="6" t="s">
         <x:v>51</x:v>
@@ -3341,22 +3326,22 @@
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B26" s="6" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="C26" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D26" s="6" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E26" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F26" s="6" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G26" s="6" t="s">
         <x:v>51</x:v>
@@ -3409,22 +3394,22 @@
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B27" s="6" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E27" s="6" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F27" s="6" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G27" s="6" t="s">
         <x:v>51</x:v>
@@ -3477,28 +3462,28 @@
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
       <x:c r="A28" s="6" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="B28" s="6" t="s">
+      <x:c r="E28" s="6" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="C28" s="6" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D28" s="6" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="E28" s="6" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F28" s="6" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="G28" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H28" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I28" s="7">
         <x:v>1</x:v>
@@ -3545,28 +3530,28 @@
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
       <x:c r="A29" s="6" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="B29" s="6" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C29" s="6" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D29" s="6" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="E29" s="6" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F29" s="6" t="s">
-        <x:v>178</x:v>
       </x:c>
       <x:c r="G29" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H29" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I29" s="7">
         <x:v>1</x:v>
@@ -3613,28 +3598,28 @@
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
       <x:c r="A30" s="6" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B30" s="6" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="C30" s="6" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D30" s="6" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="E30" s="6" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F30" s="6" t="s">
-        <x:v>181</x:v>
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>后羿碎片</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>专属材料</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str">
+        <x:v>后羿碎片</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>[材料] 后羿专属材料，当前未接入兑换流程。</x:v>
       </x:c>
       <x:c r="G30" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H30" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I30" s="7">
         <x:v>1</x:v>
@@ -3681,28 +3666,28 @@
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
       <x:c r="A31" s="6" t="s">
-        <x:v>182</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B31" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C31" s="6" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D31" s="6" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E31" s="6" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F31" s="6" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G31" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H31" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I31" s="7">
         <x:v>1</x:v>
@@ -3749,28 +3734,28 @@
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
       <x:c r="A32" s="6" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B32" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E32" s="6" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F32" s="6" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G32" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H32" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I32" s="7">
         <x:v>1</x:v>
@@ -3817,28 +3802,28 @@
     </x:row>
     <x:row r="33" ht="48" customHeight="1">
       <x:c r="A33" s="6" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B33" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E33" s="6" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F33" s="6" t="s">
-        <x:v>191</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G33" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="H33" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I33" s="7">
         <x:v>1</x:v>
